--- a/analise.xlsx
+++ b/analise.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -869,6 +869,49 @@
       </c>
       <c r="M10" t="n">
         <v>0.0825239231508158</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.01474619239047049</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.01921928370278159</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.03152435893269191</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.01910822855075774</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.05876534221260604</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.1871553355047135</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.2392974921300648</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.2346789471282301</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.2622982124510727</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.2542677581615488</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.1163024358285916</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.05667178781298553</v>
       </c>
     </row>
   </sheetData>
@@ -882,7 +925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3231,6 +3274,49 @@
         <v>0.07138444400495952</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>0.06905110958549711</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.06449111120568382</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.07891666673951679</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.06037888907723957</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.1205811121397548</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.345032219754325</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.4579677753978305</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.4617466661665175</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.4959933380285899</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0.4722544497913784</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.1980899996227688</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.1113599992460675</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/analise.xlsx
+++ b/analise.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -912,6 +912,49 @@
       </c>
       <c r="M11" t="n">
         <v>0.05667178781298553</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.0161705996567896</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.01994995443853757</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.04747338292956325</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.02492076172216702</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.09595826837717521</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.2755610057428748</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.3360436614855892</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.3447288171097537</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.3661445412785571</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.3720839182755402</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.1680520281597558</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.07652441748495163</v>
       </c>
     </row>
   </sheetData>
@@ -925,7 +968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:M56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3317,6 +3360,49 @@
         <v>0.1113599992460675</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>0.01994888865285449</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.01596888900837964</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.03365111131634977</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.01756888880497879</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.07096666627460056</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.2963844471507602</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.3853177779250675</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.4021066652403937</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.4172822203901079</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0.3958866741922167</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0.1448866645495097</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.05816888800925678</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
